--- a/static/template_documents/kwitansi_SPD.xlsx
+++ b/static/template_documents/kwitansi_SPD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>KOMISI PEMILIHAN UMUM</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Terbilang</t>
+  </si>
+  <si>
+    <t>Rp {{TERBILANG_TOTAL_DIBAYARKAN}} rupiah</t>
   </si>
   <si>
     <t xml:space="preserve">   </t>
@@ -2171,7 +2174,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="s" s="56">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D19" s="57"/>
       <c r="E19" s="26"/>
@@ -2202,7 +2205,7 @@
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" t="s" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
@@ -2216,7 +2219,7 @@
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="31"/>
       <c r="B21" t="s" s="13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -2230,7 +2233,7 @@
       <c r="L21" s="26"/>
       <c r="M21" s="26"/>
       <c r="N21" t="s" s="13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
@@ -2240,7 +2243,7 @@
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="31"/>
       <c r="B22" t="s" s="60">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
@@ -2254,7 +2257,7 @@
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
       <c r="N22" t="s" s="60">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O22" s="61"/>
       <c r="P22" s="61"/>
@@ -2264,7 +2267,7 @@
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="31"/>
       <c r="B23" t="s" s="63">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="64"/>
       <c r="D23" s="64"/>
@@ -2328,7 +2331,7 @@
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="31"/>
       <c r="B26" t="s" s="66">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="67"/>
       <c r="D26" s="67"/>
@@ -2342,7 +2345,7 @@
       <c r="L26" s="26"/>
       <c r="M26" s="26"/>
       <c r="N26" t="s" s="66">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O26" s="67"/>
       <c r="P26" s="67"/>
@@ -2352,7 +2355,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="69"/>
       <c r="B27" t="s" s="70">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="71"/>
       <c r="D27" s="71"/>
@@ -2366,7 +2369,7 @@
       <c r="L27" s="72"/>
       <c r="M27" s="72"/>
       <c r="N27" t="s" s="70">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O27" s="73"/>
       <c r="P27" s="73"/>

--- a/static/template_documents/kwitansi_SPD.xlsx
+++ b/static/template_documents/kwitansi_SPD.xlsx
@@ -49,22 +49,45 @@
     <t>M.a.</t>
   </si>
   <si>
-    <t>Sudah terima dari Komisi Pemilihan Umum Provinsi Sulawesi Tenggara</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Book Antiqua"/>
+      </rPr>
+      <t>Sudah terima dari Komisi Pemilihan Umum Provinsi Sulawesi Tenggara</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Book Antiqua"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Uang sebesar : </t>
+  </si>
+  <si>
+    <t>Rp {{TOTAL_DIBAYARKAN}}</t>
+  </si>
+  <si>
+    <t>Guna Pembayaran</t>
+  </si>
+  <si>
+    <t>biaya perjalanan dinas (lumpsum)</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uang sebesar : </t>
-  </si>
-  <si>
-    <t>Rp {{TOTAL_DIBAYARKAN}}</t>
-  </si>
-  <si>
-    <t>Guna Pembayaran</t>
-  </si>
-  <si>
-    <t>biaya perjalanan dinas (lumpsum)</t>
   </si>
   <si>
     <t>kekurangan biaya perjalanan dinas</t>
@@ -128,10 +151,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="&quot; Rp&quot;* #,##0&quot; &quot;;&quot; Rp&quot;* (#,##0);&quot; Rp&quot;* &quot;- &quot;"/>
-    <numFmt numFmtId="60" formatCode="dddd&quot;, &quot;mmmm&quot; &quot;dd&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="59" formatCode="dddd&quot;, &quot;mmmm&quot; &quot;dd&quot;, &quot;yyyy"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -417,7 +439,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -517,24 +539,27 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="8" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
@@ -568,11 +593,8 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="60" fontId="11" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="11" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -583,14 +605,11 @@
     <xf numFmtId="49" fontId="13" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="60" fontId="13" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="13" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="14" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1986,16 +2005,14 @@
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" t="s" s="15">
-        <v>13</v>
-      </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="26"/>
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
@@ -2006,15 +2023,15 @@
       <c r="A12" s="31"/>
       <c r="B12" s="26"/>
       <c r="C12" t="s" s="15">
+        <v>13</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" t="s" s="35">
         <v>14</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" t="s" s="34">
-        <v>15</v>
-      </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="26"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
@@ -2031,8 +2048,8 @@
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="26"/>
       <c r="H13" s="12"/>
       <c r="I13" s="37"/>
@@ -2049,48 +2066,48 @@
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="31"/>
       <c r="B14" s="26"/>
-      <c r="C14" t="s" s="39">
+      <c r="C14" t="s" s="40">
+        <v>15</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="26"/>
+      <c r="F14" t="s" s="42">
         <v>16</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="26"/>
-      <c r="F14" t="s" s="41">
-        <v>17</v>
-      </c>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
       <c r="N14" t="s" s="13">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O14" s="14"/>
-      <c r="P14" s="44"/>
+      <c r="P14" s="45"/>
       <c r="Q14" s="26"/>
       <c r="R14" s="30"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="31"/>
       <c r="B15" s="26"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="26"/>
-      <c r="F15" t="s" s="45">
+      <c r="F15" t="s" s="46">
         <v>18</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
       <c r="N15" s="14"/>
       <c r="O15" s="26"/>
-      <c r="P15" s="44"/>
+      <c r="P15" s="45"/>
       <c r="Q15" s="26"/>
       <c r="R15" s="30"/>
     </row>
@@ -2122,19 +2139,19 @@
       <c r="C17" t="s" s="15">
         <v>20</v>
       </c>
-      <c r="D17" t="s" s="49">
+      <c r="D17" t="s" s="50">
         <v>21</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
       <c r="G17" s="14"/>
       <c r="H17" t="s" s="15">
         <v>22</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
       <c r="M17" s="26"/>
       <c r="N17" s="26"/>
       <c r="O17" s="26"/>
@@ -2176,29 +2193,29 @@
       <c r="C19" t="s" s="56">
         <v>26</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
       <c r="L19" t="s" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M19" s="26"/>
       <c r="N19" s="14"/>
       <c r="O19" s="14"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
-      <c r="R19" s="58"/>
+      <c r="R19" s="57"/>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="31"/>
       <c r="B20" s="26"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -2238,42 +2255,42 @@
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
-      <c r="R21" s="58"/>
+      <c r="R21" s="57"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="31"/>
-      <c r="B22" t="s" s="60">
+      <c r="B22" t="s" s="59">
         <v>30</v>
       </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
       <c r="J22" s="26"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
-      <c r="N22" t="s" s="60">
+      <c r="N22" t="s" s="59">
         <v>31</v>
       </c>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="62"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="61"/>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="31"/>
-      <c r="B23" t="s" s="63">
+      <c r="B23" t="s" s="62">
         <v>32</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
@@ -2289,11 +2306,11 @@
     <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="31"/>
       <c r="B24" s="26"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
@@ -2308,14 +2325,14 @@
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" t="s" s="24">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" s="26"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
@@ -2330,60 +2347,59 @@
     </row>
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="31"/>
-      <c r="B26" t="s" s="66">
+      <c r="B26" t="s" s="65">
         <v>33</v>
       </c>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
       <c r="M26" s="26"/>
-      <c r="N26" t="s" s="66">
+      <c r="N26" t="s" s="65">
         <v>34</v>
       </c>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="68"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="67"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="69"/>
-      <c r="B27" t="s" s="70">
+      <c r="A27" s="68"/>
+      <c r="B27" t="s" s="69">
         <v>35</v>
       </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" t="s" s="70">
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" t="s" s="69">
         <v>36</v>
       </c>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="73"/>
-      <c r="R27" s="74"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="N26:R26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="N27:R27"/>
-    <mergeCell ref="C19:D19"/>
     <mergeCell ref="N19:R19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B21:F21"/>
@@ -2400,9 +2416,11 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="I12:R13"/>
     <mergeCell ref="H17:L17"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="C11:M11"/>
   </mergeCells>
   <pageMargins left="0.314961" right="0.19685" top="0.748031" bottom="0.748031" header="0.314961" footer="0.314961"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="80" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
